--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_JAEN PARAÍSO INTERIOR CB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_JAEN PARAÍSO INTERIOR CB.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4214</v>
+        <v>4.406099999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4829</v>
+        <v>4.6753</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0613999999999999</v>
+        <v>-0.2692999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.8478</v>
+        <v>-1.8477</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7639</v>
+        <v>4.7827</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.6116</v>
+        <v>-6.6304</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3228000000000002</v>
+        <v>0.4372</v>
       </c>
       <c r="K2" t="n">
-        <v>3.817</v>
+        <v>3.8904</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.4942</v>
+        <v>-3.4532</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1705</v>
+        <v>-2.2849</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9469000000000001</v>
+        <v>0.8923</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.1173</v>
+        <v>-3.1771</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6145</v>
+        <v>0.6073999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R2" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S2" t="n">
-        <v>3.33</v>
+        <v>3.290500000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>2.773</v>
+        <v>2.7852</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5569999999999999</v>
+        <v>0.5052</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3247</v>
+        <v>2.356</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4356</v>
+        <v>3.4774</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.111</v>
+        <v>-1.1214</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1585</v>
+        <v>3.2135</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9102</v>
+        <v>1.1526</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2482</v>
+        <v>2.061</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3709</v>
+        <v>2.3853</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6967000000000001</v>
+        <v>-0.6921</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0677</v>
+        <v>3.0774</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9789</v>
+        <v>3.0953</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1402000000000001</v>
+        <v>0.1949000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8387</v>
+        <v>2.9003</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6078999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8369</v>
+        <v>-0.887</v>
       </c>
       <c r="O3" t="n">
-        <v>0.229</v>
+        <v>0.177</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.326000000000001</v>
+        <v>-5.2638</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0727</v>
+        <v>3.0368</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0249</v>
+        <v>-1.0216</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2843</v>
+        <v>-0.2496</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7405999999999999</v>
+        <v>-0.772</v>
       </c>
       <c r="V3" t="n">
-        <v>4.0659</v>
+        <v>4.0768</v>
       </c>
       <c r="W3" t="n">
-        <v>3.5418</v>
+        <v>3.5706</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5241</v>
+        <v>0.5062</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8209</v>
+        <v>2.9112</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5228</v>
+        <v>4.7953</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7019</v>
+        <v>-1.884</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6376</v>
+        <v>1.7085</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1384</v>
+        <v>-0.0819</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7761</v>
+        <v>1.7904</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4079</v>
+        <v>2.5745</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9772999999999999</v>
+        <v>1.0818</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4306</v>
+        <v>1.4926</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7702</v>
+        <v>-0.8661000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1157</v>
+        <v>-1.1639</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3455000000000001</v>
+        <v>0.2978000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.229</v>
+        <v>-1.2148</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2637</v>
+        <v>-1.2507</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9239999999999999</v>
+        <v>-0.888</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3396</v>
+        <v>-0.3626</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="W4" t="n">
-        <v>4.268</v>
+        <v>4.323399999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.8454</v>
+        <v>-2.8822</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6432</v>
+        <v>1.7082</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9338</v>
+        <v>3.1872</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2906</v>
+        <v>-1.479</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7048</v>
+        <v>2.7632</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8746</v>
+        <v>-0.8322999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5792</v>
+        <v>3.5957</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4752</v>
+        <v>4.6481</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7343</v>
+        <v>-0.6375</v>
       </c>
       <c r="L5" t="n">
-        <v>5.2095</v>
+        <v>5.2856</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7705</v>
+        <v>-1.8849</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1402</v>
+        <v>-0.1949</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6303</v>
+        <v>-1.6899</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.1063</v>
+        <v>-2.0875</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7108</v>
+        <v>-0.6752</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3955</v>
+        <v>-1.4124</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0447</v>
+        <v>1.0325</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3779</v>
+        <v>-0.4086</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3348</v>
+        <v>1.2915</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9097</v>
+        <v>1.6889</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5749</v>
+        <v>-0.3974</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0958</v>
+        <v>0.6112</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8169000000000001</v>
+        <v>0.8306</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2788000000000002</v>
+        <v>-0.2194</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5215</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1.403</v>
+        <v>0.05930000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1185</v>
+        <v>0.0398</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4257000000000001</v>
+        <v>0.5123000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.586</v>
+        <v>0.7714</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1603000000000001</v>
+        <v>-0.2591</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6145</v>
+        <v>0.6073999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2291</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8436</v>
+        <v>0.6073999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0918</v>
+        <v>0.07289999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8296</v>
+        <v>0.1488</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2622</v>
+        <v>-0.0759</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4674</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2123999999999999</v>
+        <v>1.4411</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2551</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3139</v>
+        <v>1.2625</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6685</v>
+        <v>2.0169</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3546</v>
+        <v>-0.7545000000000002</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6226</v>
+        <v>1.0728</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8388</v>
+        <v>0.8295999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2162</v>
+        <v>0.2432000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.098</v>
+        <v>1.5791</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0585</v>
+        <v>1.4599</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0395</v>
+        <v>0.1193</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5246</v>
+        <v>-0.5064000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7803</v>
+        <v>-0.6303</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2558</v>
+        <v>0.1238999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6145</v>
+        <v>0.6073999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.2147</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6145</v>
+        <v>1.8221</v>
       </c>
       <c r="S7" t="n">
-        <v>0.07669999999999999</v>
+        <v>2.056</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1478</v>
+        <v>1.8389</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07089999999999999</v>
+        <v>0.2171000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.4736</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4227</v>
+        <v>-0.1865000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4227</v>
+        <v>-2.2871</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1111</v>
+        <v>-1.1617</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6083</v>
+        <v>-0.5835</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5029000000000001</v>
+        <v>-0.5782</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4577</v>
+        <v>-1.4886</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4078</v>
+        <v>-1.4225</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04990000000000006</v>
+        <v>-0.06609999999999994</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3226</v>
+        <v>-0.3151</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5992</v>
+        <v>-0.5932999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2766</v>
+        <v>0.2783</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.135</v>
+        <v>-1.1736</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8087000000000001</v>
+        <v>-0.8291999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3264</v>
+        <v>-0.3444</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2049</v>
+        <v>0.2024</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2776</v>
+        <v>0.2822</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7386</v>
+        <v>0.7439</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.461</v>
+        <v>-0.4616</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1359</v>
+        <v>-0.1577</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1359</v>
+        <v>-0.1577</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8334</v>
+        <v>-1.8937</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2037</v>
+        <v>-2.1492</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3704000000000001</v>
+        <v>0.2554</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4232</v>
+        <v>-0.4677</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09460000000000002</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5178</v>
+        <v>-0.5476000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3922</v>
+        <v>0.3961</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2342</v>
+        <v>0.2371</v>
       </c>
       <c r="L9" t="n">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8153999999999999</v>
+        <v>-0.8637999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1396</v>
+        <v>-0.1572</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6758</v>
+        <v>-0.7066</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1719</v>
+        <v>1.1611</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1733</v>
+        <v>1.1798</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.001299999999999968</v>
+        <v>-0.01879999999999993</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3531</v>
+        <v>-1.3723</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6566</v>
+        <v>-0.6840000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3109</v>
+        <v>-2.297</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2497</v>
+        <v>-2.1547</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0612</v>
+        <v>-0.1423</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8464999999999999</v>
+        <v>0.8331999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.312</v>
+        <v>0.2972</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5345</v>
+        <v>0.5359999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2848</v>
+        <v>1.3148</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0058</v>
+        <v>0.0191</v>
       </c>
       <c r="L10" t="n">
-        <v>1.279</v>
+        <v>1.2956</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4383</v>
+        <v>-0.4815999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3062</v>
+        <v>0.2782</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7444000000000001</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1703</v>
+        <v>-0.1665</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7037</v>
+        <v>-0.6836</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5334</v>
+        <v>0.5172</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9385</v>
+        <v>-0.9393</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0819</v>
+        <v>-3.0996</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7515</v>
+        <v>-1.6541</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3304</v>
+        <v>-1.4456</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.7012</v>
+        <v>-4.7016</v>
       </c>
       <c r="H11" t="n">
-        <v>1.767</v>
+        <v>1.7596</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.4682</v>
+        <v>-6.4612</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1755</v>
+        <v>-2.1141</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9906</v>
+        <v>2.015</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.166</v>
+        <v>-4.129099999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5256</v>
+        <v>-2.5875</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2234</v>
+        <v>-0.2554</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3022</v>
+        <v>-2.3322</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3555</v>
+        <v>-0.3497</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4084</v>
+        <v>-0.3861</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0529</v>
+        <v>0.03639999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2786</v>
+        <v>-0.2754</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.111</v>
+        <v>-1.1214</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0589</v>
+        <v>-4.119</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4429</v>
+        <v>-3.3502</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6159</v>
+        <v>-0.7688</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3255</v>
+        <v>-4.3475</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.285</v>
+        <v>-1.2849</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0406</v>
+        <v>-3.0626</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.5278</v>
+        <v>-3.48</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9779</v>
+        <v>-0.9502</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.55</v>
+        <v>-2.5298</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7976000000000001</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3070000000000001</v>
+        <v>-0.3347</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4906</v>
+        <v>-0.5327000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R12" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5869</v>
+        <v>2.5683</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1167</v>
+        <v>2.1261</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4703000000000001</v>
+        <v>0.4422</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.7542</v>
+        <v>-3.7571</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.8027</v>
+        <v>-0.7816</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.9515</v>
+        <v>-2.9755</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4253</v>
+        <v>-6.3655</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8296</v>
+        <v>-3.5275</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5957</v>
+        <v>-2.838</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6614</v>
+        <v>-3.622</v>
       </c>
       <c r="H13" t="n">
-        <v>2.501</v>
+        <v>2.5476</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.1624</v>
+        <v>-6.1696</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6629</v>
+        <v>-1.4982</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4741</v>
+        <v>2.5839</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.137</v>
+        <v>-4.0821</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9985</v>
+        <v>-2.1238</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02690000000000001</v>
+        <v>-0.0363</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.0254</v>
+        <v>-2.0876</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8678</v>
+        <v>2.8344</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9285</v>
+        <v>-0.9295</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1776</v>
+        <v>-1.1338</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2492</v>
+        <v>0.2042</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4179</v>
+        <v>0.413</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1321</v>
+        <v>4.1657</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.7142</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.1288</v>
+        <v>-4.1435</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3422</v>
+        <v>4.097</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.470899999999999</v>
+        <v>-8.2407</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.1386</v>
+        <v>-7.1009</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6917</v>
+        <v>6.813400000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.8304</v>
+        <v>-13.9142</v>
       </c>
       <c r="J14" t="n">
-        <v>5.792500000000002</v>
+        <v>6.736799999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>8.789300000000001</v>
+        <v>9.360400000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.9968</v>
+        <v>-2.623699999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.9306</v>
+        <v>-13.8377</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0972</v>
+        <v>-2.547</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.8334</v>
+        <v>-11.2905</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.0244</v>
+        <v>-1.0121</v>
       </c>
       <c r="Q14" t="n">
-        <v>-25.6058</v>
+        <v>-25.3067</v>
       </c>
       <c r="R14" t="n">
-        <v>24.5814</v>
+        <v>24.2946</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6857</v>
+        <v>3.6255</v>
       </c>
       <c r="T14" t="n">
-        <v>4.5702</v>
+        <v>4.806399999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8839000000000002</v>
+        <v>-1.181</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3482000000000003</v>
+        <v>0.3439999999999987</v>
       </c>
       <c r="W14" t="n">
-        <v>17.5858</v>
+        <v>17.8598</v>
       </c>
       <c r="X14" t="n">
-        <v>-17.2378</v>
+        <v>-17.5157</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_JAEN PARAÍSO INTERIOR CB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_JAEN PARAÍSO INTERIOR CB.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>G. VERGARA HARBOE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.406099999999999</v>
+        <v>4.1515</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6753</v>
+        <v>5.6897</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2692999999999999</v>
+        <v>-1.5383</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.8477</v>
+        <v>1.7085</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7827</v>
+        <v>-0.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.6304</v>
+        <v>1.7904</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4372</v>
+        <v>2.5745</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8904</v>
+        <v>1.0818</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.4532</v>
+        <v>1.4926</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.2849</v>
+        <v>-0.8661000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8923</v>
+        <v>-1.1639</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.1771</v>
+        <v>0.2978000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6073999999999999</v>
+        <v>1.0123</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0245</v>
+        <v>-1.2148</v>
       </c>
       <c r="R2" t="n">
-        <v>2.6319</v>
+        <v>2.227</v>
       </c>
       <c r="S2" t="n">
-        <v>3.290500000000001</v>
+        <v>-0.01039999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7852</v>
+        <v>0.006500000000000006</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5052</v>
+        <v>-0.0169</v>
       </c>
       <c r="V2" t="n">
-        <v>2.356</v>
+        <v>1.4411</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4774</v>
+        <v>4.323399999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1214</v>
+        <v>-2.8822</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2135</v>
+        <v>4.033200000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1526</v>
+        <v>1.8395</v>
       </c>
       <c r="F3" t="n">
-        <v>2.061</v>
+        <v>2.1937</v>
       </c>
       <c r="G3" t="n">
         <v>2.3853</v>
@@ -688,13 +688,13 @@
         <v>3.0368</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0216</v>
+        <v>-0.202</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2496</v>
+        <v>0.4374</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.772</v>
+        <v>-0.6393</v>
       </c>
       <c r="V3" t="n">
         <v>4.0768</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. VERGARA HARBOE</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9112</v>
+        <v>3.208</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7953</v>
+        <v>3.9779</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.884</v>
+        <v>-0.7699</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7085</v>
+        <v>2.7632</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0819</v>
+        <v>-0.8322999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7904</v>
+        <v>3.5957</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5745</v>
+        <v>4.6481</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0818</v>
+        <v>-0.6375</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4926</v>
+        <v>5.2856</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8661000000000001</v>
+        <v>-1.8849</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1639</v>
+        <v>-0.1949</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2978000000000001</v>
+        <v>-1.6899</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0123</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2148</v>
+        <v>-2.227</v>
       </c>
       <c r="R4" t="n">
         <v>2.227</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2507</v>
+        <v>-0.5878</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.888</v>
+        <v>0.1155</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3626</v>
+        <v>-0.7033</v>
       </c>
       <c r="V4" t="n">
+        <v>1.0325</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.4411</v>
       </c>
-      <c r="W4" t="n">
-        <v>4.323399999999999</v>
-      </c>
       <c r="X4" t="n">
-        <v>-2.8822</v>
+        <v>-0.4086</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7082</v>
+        <v>2.7864</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1872</v>
+        <v>3.1822</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.479</v>
+        <v>-0.3957999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7632</v>
+        <v>-1.8477</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8322999999999999</v>
+        <v>4.7827</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5957</v>
+        <v>-6.6304</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6481</v>
+        <v>0.4372</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6375</v>
+        <v>3.8904</v>
       </c>
       <c r="L5" t="n">
-        <v>5.2856</v>
+        <v>-3.4532</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8849</v>
+        <v>-2.2849</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1949</v>
+        <v>0.8923</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6899</v>
+        <v>-3.1771</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.6073999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.227</v>
+        <v>-2.0245</v>
       </c>
       <c r="R5" t="n">
-        <v>2.227</v>
+        <v>2.6319</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.0875</v>
+        <v>1.6707</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6752</v>
+        <v>1.2921</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4124</v>
+        <v>0.3786</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0325</v>
+        <v>2.356</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4411</v>
+        <v>3.4774</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4086</v>
+        <v>-1.1214</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2915</v>
+        <v>1.6318</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6889</v>
+        <v>2.0004</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3974</v>
+        <v>-0.3686</v>
       </c>
       <c r="G6" t="n">
         <v>0.6112</v>
@@ -922,13 +922,13 @@
         <v>0.6073999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07289999999999999</v>
+        <v>0.4131</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1488</v>
+        <v>0.4601999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0759</v>
+        <v>-0.04709999999999998</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2625</v>
+        <v>-0.1666000000000003</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0169</v>
+        <v>1.1466</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7545000000000002</v>
+        <v>-1.3132</v>
       </c>
       <c r="G7" t="n">
         <v>1.0728</v>
@@ -1000,13 +1000,13 @@
         <v>1.8221</v>
       </c>
       <c r="S7" t="n">
-        <v>2.056</v>
+        <v>0.6268999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8389</v>
+        <v>0.9686999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2171000000000001</v>
+        <v>-0.3418</v>
       </c>
       <c r="V7" t="n">
         <v>-2.4736</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1617</v>
+        <v>-1.4834</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5835</v>
+        <v>-1.5716</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5782</v>
+        <v>0.0882</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4886</v>
+        <v>0.8331999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4225</v>
+        <v>0.2972</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06609999999999994</v>
+        <v>0.5359999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3151</v>
+        <v>1.3148</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5932999999999999</v>
+        <v>0.0191</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2783</v>
+        <v>1.2956</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1736</v>
+        <v>-0.4815999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8291999999999999</v>
+        <v>0.2782</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3444</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2024</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0123</v>
+        <v>-3.0368</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2147</v>
+        <v>1.0123</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2822</v>
+        <v>0.6472</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7439</v>
+        <v>-0.1006</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4616</v>
+        <v>0.7477</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1577</v>
+        <v>-0.9393</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1577</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8937</v>
+        <v>-1.5425</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1492</v>
+        <v>-1.3101</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2554</v>
+        <v>-0.2323999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4677</v>
+        <v>-1.4886</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07980000000000001</v>
+        <v>-1.4225</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5476000000000001</v>
+        <v>-0.06609999999999994</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3961</v>
+        <v>-0.3151</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2371</v>
+        <v>-0.5932999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.159</v>
+        <v>0.2783</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8637999999999999</v>
+        <v>-1.1736</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1572</v>
+        <v>-0.8291999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7066</v>
+        <v>-0.3444</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2147</v>
+        <v>0.2024</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0368</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8221</v>
+        <v>1.2147</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1611</v>
+        <v>-0.09860000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1798</v>
+        <v>0.0171</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.01879999999999993</v>
+        <v>-0.1159</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3723</v>
+        <v>-0.1577</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6883</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.1577</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.297</v>
+        <v>-2.4128</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1547</v>
+        <v>-2.6682</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1423</v>
+        <v>0.2554999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8331999999999999</v>
+        <v>-0.4677</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2972</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5359999999999999</v>
+        <v>-0.5476000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3148</v>
+        <v>0.3961</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0191</v>
+        <v>0.2371</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2956</v>
+        <v>0.159</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4815999999999999</v>
+        <v>-0.8637999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2782</v>
+        <v>-0.1572</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7066</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0245</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.0368</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0123</v>
+        <v>1.8221</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1665</v>
+        <v>0.642</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6836</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5172</v>
+        <v>-0.01880000000000004</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9393</v>
+        <v>-1.3723</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2509</v>
+        <v>-0.6883</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1902</v>
+        <v>-0.6840000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0996</v>
+        <v>-2.6492</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6541</v>
+        <v>-1.1748</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4456</v>
+        <v>-1.4744</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7016</v>
@@ -1312,13 +1312,13 @@
         <v>2.227</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3497</v>
+        <v>0.1007</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3861</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03639999999999999</v>
+        <v>0.007500000000000007</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2754</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>C. FIELDS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.119</v>
+        <v>-4.6577</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3502</v>
+        <v>-2.01</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7688</v>
+        <v>-2.6477</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3475</v>
+        <v>-3.622</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2849</v>
+        <v>2.5476</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0626</v>
+        <v>-6.1696</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.48</v>
+        <v>-1.4982</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9502</v>
+        <v>2.5839</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5298</v>
+        <v>-4.0821</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-2.1238</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3347</v>
+        <v>-0.0363</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5327000000000001</v>
+        <v>-2.0876</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4172</v>
+        <v>-2.227</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2147</v>
+        <v>-5.0613</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6319</v>
+        <v>2.8344</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5683</v>
+        <v>0.7782</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1261</v>
+        <v>0.3836</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4422</v>
+        <v>0.3946000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.7571</v>
+        <v>0.413</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7816</v>
+        <v>4.1657</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.9755</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. FIELDS</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3655</v>
+        <v>-5.0177</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5275</v>
+        <v>-4.3641</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.838</v>
+        <v>-0.6536</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.622</v>
+        <v>-4.3475</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5476</v>
+        <v>-1.2849</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.1696</v>
+        <v>-3.0626</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4982</v>
+        <v>-3.48</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5839</v>
+        <v>-0.9502</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0821</v>
+        <v>-2.5298</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1238</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0363</v>
+        <v>-0.3347</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.0876</v>
+        <v>-0.5327000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.227</v>
+        <v>1.4172</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.0613</v>
+        <v>-1.2147</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8344</v>
+        <v>2.6319</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9295</v>
+        <v>1.6697</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1338</v>
+        <v>1.1123</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2042</v>
+        <v>0.5575</v>
       </c>
       <c r="V13" t="n">
-        <v>0.413</v>
+        <v>-3.7571</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1657</v>
+        <v>-0.7816</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.7527</v>
+        <v>-2.9755</v>
       </c>
     </row>
     <row r="14">
@@ -1501,28 +1501,28 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.1435</v>
+        <v>-2.119</v>
       </c>
       <c r="E14" t="n">
-        <v>4.097</v>
+        <v>4.737500000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.2407</v>
+        <v>-6.8565</v>
       </c>
       <c r="G14" t="n">
         <v>-7.1009</v>
       </c>
       <c r="H14" t="n">
-        <v>6.813400000000001</v>
+        <v>6.8134</v>
       </c>
       <c r="I14" t="n">
         <v>-13.9142</v>
       </c>
       <c r="J14" t="n">
-        <v>6.736799999999998</v>
+        <v>6.736799999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>9.360400000000002</v>
+        <v>9.3604</v>
       </c>
       <c r="L14" t="n">
         <v>-2.623699999999999</v>
@@ -1546,16 +1546,16 @@
         <v>24.2946</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6255</v>
+        <v>5.649699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.806399999999999</v>
+        <v>5.446800000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.181</v>
+        <v>0.2028</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3439999999999987</v>
+        <v>0.3439999999999968</v>
       </c>
       <c r="W14" t="n">
         <v>17.8598</v>
